--- a/data/trans_dic/P79$hipoteca_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P79$hipoteca_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,31</t>
+          <t>0,39; 2,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,79</t>
+          <t>0,31; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,72</t>
+          <t>0,48; 1,68</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,53</t>
+          <t>0,87; 3,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,43</t>
+          <t>0,38; 2,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,54</t>
+          <t>0,88; 2,46</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,8</t>
+          <t>0,43; 2,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,56</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,68</t>
+          <t>0,47; 1,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,33</t>
+          <t>0,45; 1,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,32</t>
+          <t>0,57; 1,36</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,97</t>
+          <t>0,53; 1,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,38</t>
+          <t>0,41; 1,32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,37</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,52</t>
+          <t>0,06; 1,17</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,36</t>
+          <t>0,74; 1,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,0</t>
+          <t>0,51; 1,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,03</t>
+          <t>0,67; 1,11</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9826</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1963; 11581</t>
+          <t>2130; 13399</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1360; 7898</t>
+          <t>1505; 9078</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4251; 16174</t>
+          <t>4963; 17258</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>13639</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3956; 15738</t>
+          <t>4126; 18334</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1486; 9200</t>
+          <t>1594; 9802</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7159; 20947</t>
+          <t>7903; 22046</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>735; 11854</t>
+          <t>1994; 11892</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1022; 12827</t>
+          <t>2082; 12907</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>17972</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4545; 17047</t>
+          <t>5266; 19308</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2453; 12632</t>
+          <t>3715; 13117</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9335; 25826</t>
+          <t>11064; 26433</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10146</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 10069</t>
+          <t>0; 7743</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4006; 14628</t>
+          <t>4221; 15292</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4880; 16536</t>
+          <t>5471; 17626</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>3163</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 801</t>
+          <t>0; 10278</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3979</t>
+          <t>0; 5760</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>169; 4837</t>
+          <t>620; 11779</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20149; 44553</t>
+          <t>24547; 49558</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16115; 34033</t>
+          <t>17777; 34956</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39356; 68612</t>
+          <t>45634; 76108</t>
         </is>
       </c>
     </row>
